--- a/Intro_files/Beurteilungsvorlage.xlsx
+++ b/Intro_files/Beurteilungsvorlage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\ucloud2\Lehre\Personal Coaching Script\PersonalCoaching_Script\Intro_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paedd\OneDrive\Documents\GitHub\PersonalCoaching_Script\Intro_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39EFD0F-796E-45D9-B739-E26C0FB5FD94}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28536C2-9110-46B0-AB29-690871965206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{715A95F7-DA77-4098-9B8F-DCFA90ADB0C9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{715A95F7-DA77-4098-9B8F-DCFA90ADB0C9}"/>
   </bookViews>
   <sheets>
     <sheet name="SSA" sheetId="3" r:id="rId1"/>
@@ -59,9 +59,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="87">
   <si>
-    <t>MAX MAXIMUM</t>
-  </si>
-  <si>
     <t>NOTE</t>
   </si>
   <si>
@@ -337,6 +334,9 @@
   <si>
     <t>Peer-Review (10P)</t>
   </si>
+  <si>
+    <t>Max Effort</t>
+  </si>
 </sst>
 </file>
 
@@ -347,7 +347,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -744,22 +744,61 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -771,12 +810,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -797,39 +830,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1170,96 +1170,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BAE265-16B2-4831-A793-A5E30A21D8A1}">
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.4140625" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.4140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.75" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" style="5" customWidth="1"/>
     <col min="3" max="3" width="15" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.58203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="11.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.83203125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="15.75" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" style="5" customWidth="1"/>
-    <col min="11" max="11" width="14.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.58203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="9.25" style="5" customWidth="1"/>
-    <col min="18" max="18" width="7.4140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.4140625" style="5"/>
+    <col min="4" max="4" width="13.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.81640625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="15.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" style="5" customWidth="1"/>
+    <col min="11" max="11" width="14.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.26953125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="7.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.453125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="6" customFormat="1" ht="52.5" customHeight="1">
+    <row r="1" spans="1:20" s="6" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="K1" s="7" t="s">
+      <c r="M1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="N1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="R1" s="7" t="s">
+      <c r="S1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="T1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="18.649999999999999" customHeight="1">
+    </row>
+    <row r="2" spans="1:20" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="C2" s="8">
         <v>1</v>
@@ -1327,56 +1327,56 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535EDAC6-2B4F-49F4-BCA7-6B666EE7443D}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.1640625" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="26">
+    <row r="1" spans="1:10" ht="26" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="21.75" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="C2" s="10">
         <v>10</v>
@@ -1416,526 +1416,526 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8925FC-4407-41A6-8D22-7170C00831DD}">
   <dimension ref="A1:F38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.4140625" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.4140625" style="15"/>
-    <col min="2" max="2" width="16.25" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.25" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.58203125" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="83.4140625" style="16" customWidth="1"/>
-    <col min="6" max="16384" width="11.4140625" style="15"/>
+    <col min="1" max="1" width="11.453125" style="15"/>
+    <col min="2" max="2" width="16.26953125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="83.453125" style="16" customWidth="1"/>
+    <col min="6" max="16384" width="11.453125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.5">
-      <c r="A1" s="58" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="60"/>
-    </row>
-    <row r="2" spans="1:6" ht="35.25" customHeight="1" thickBot="1">
+    <row r="1" spans="1:6" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="48"/>
+    </row>
+    <row r="2" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21"/>
       <c r="B2" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="D2" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="40">
+        <v>3</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="57"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="27"/>
+      <c r="F4" s="45"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="57"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="F5" s="45"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="57"/>
+      <c r="B6" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="42">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="57"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="43"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="57"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="43"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="57"/>
+      <c r="B9" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="41">
+        <v>4</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="57"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="45"/>
+    </row>
+    <row r="11" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="57"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="45"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="57"/>
+      <c r="B12" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="42">
+        <v>4</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="28">
-      <c r="A3" s="43" t="s">
+      <c r="F12" s="43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="57"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="43"/>
+    </row>
+    <row r="14" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="57"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="43"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="57"/>
+      <c r="B15" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="41">
+        <v>4</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="57"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="45"/>
+    </row>
+    <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="57"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="45"/>
+    </row>
+    <row r="18" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="57"/>
+      <c r="B18" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="42">
+        <v>4</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="57"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="43"/>
+    </row>
+    <row r="20" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="A20" s="57"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="43"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="57"/>
+      <c r="B21" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="41">
+        <v>3</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="57"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="27"/>
+      <c r="F22" s="45"/>
+    </row>
+    <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="57"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="45"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="57"/>
+      <c r="B24" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="42">
+        <v>3</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="57"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="17"/>
+      <c r="F25" s="43"/>
+    </row>
+    <row r="26" spans="1:6" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="58"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="50"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="63">
-        <v>3</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="57">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="44"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="39"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="44"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="39"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="44"/>
-      <c r="B6" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="55">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="44"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="40"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="44"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="9" t="s">
+      <c r="C27" s="40">
+        <v>5</v>
+      </c>
+      <c r="D27" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="40"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="44"/>
-      <c r="B9" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="56">
+      <c r="E27" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="61"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="27"/>
+      <c r="F28" s="45"/>
+    </row>
+    <row r="29" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="61"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="45"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="61"/>
+      <c r="B30" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="42">
+        <v>5</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="17"/>
+      <c r="F30" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="61"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="17"/>
+      <c r="F31" s="43"/>
+    </row>
+    <row r="32" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="62"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="50"/>
+    </row>
+    <row r="33" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="40">
         <v>4</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D33" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F33" s="44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="64"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="39">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="44"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="28" t="s">
+      <c r="E34" s="27"/>
+      <c r="F34" s="45"/>
+    </row>
+    <row r="35" spans="1:6" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="65"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="39"/>
-    </row>
-    <row r="11" spans="1:6" ht="42">
-      <c r="A11" s="44"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="39"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="44"/>
-      <c r="B12" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="55">
-        <v>4</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="40">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="44"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="40"/>
-    </row>
-    <row r="14" spans="1:6" ht="28">
-      <c r="A14" s="44"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="40"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="44"/>
-      <c r="B15" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="56">
-        <v>4</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="39">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="44"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="39"/>
-    </row>
-    <row r="17" spans="1:6" ht="28">
-      <c r="A17" s="44"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="39"/>
-    </row>
-    <row r="18" spans="1:6" ht="70">
-      <c r="A18" s="44"/>
-      <c r="B18" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="55">
-        <v>4</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="40">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="44"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" s="17"/>
-      <c r="F19" s="40"/>
-    </row>
-    <row r="20" spans="1:6" ht="56">
-      <c r="A20" s="44"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="40"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="44"/>
-      <c r="B21" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="56">
-        <v>3</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="44"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="39"/>
-    </row>
-    <row r="23" spans="1:6" ht="28">
-      <c r="A23" s="44"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="39"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="44"/>
-      <c r="B24" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="55">
-        <v>3</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="40">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="44"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="17"/>
-      <c r="F25" s="40"/>
-    </row>
-    <row r="26" spans="1:6" ht="42.5" thickBot="1">
-      <c r="A26" s="45"/>
-      <c r="B26" s="47"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="62"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="63">
-        <v>5</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F27" s="57">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="50"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="27"/>
-      <c r="F28" s="39"/>
-    </row>
-    <row r="29" spans="1:6" ht="28">
-      <c r="A29" s="50"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="F29" s="39"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="50"/>
-      <c r="B30" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="55">
-        <v>5</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E30" s="17"/>
-      <c r="F30" s="40">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="50"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="40"/>
-    </row>
-    <row r="32" spans="1:6" ht="28.5" thickBot="1">
-      <c r="A32" s="51"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E32" s="19" t="s">
+      <c r="E35" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="F32" s="62"/>
-    </row>
-    <row r="33" spans="1:6" ht="27" customHeight="1">
-      <c r="A33" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="63">
-        <v>4</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F33" s="57">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="53"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="E34" s="27"/>
-      <c r="F34" s="39"/>
-    </row>
-    <row r="35" spans="1:6" ht="42.75" customHeight="1" thickBot="1">
-      <c r="A35" s="54"/>
-      <c r="B35" s="48"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="E35" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" s="61"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="B37" s="38"/>
+      <c r="F35" s="49"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="55"/>
       <c r="C37" s="31">
         <f>SUM(C33,C3:C26)</f>
         <v>30</v>
       </c>
       <c r="D37" s="18"/>
       <c r="E37" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F37" s="33">
         <f>SUM(F33,F3:F26)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="37"/>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="54"/>
       <c r="C38" s="36">
         <f>SUM(C27:C32)</f>
         <v>10</v>
       </c>
       <c r="D38" s="18"/>
       <c r="E38" s="34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F38" s="35">
         <f>SUM(F27:F32)</f>
@@ -1944,13 +1944,22 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="A3:A26"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="A27:A32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="B18:B20"/>
     <mergeCell ref="F6:F8"/>
     <mergeCell ref="F3:F5"/>
     <mergeCell ref="A1:F1"/>
@@ -1967,22 +1976,13 @@
     <mergeCell ref="C27:C29"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="B24:B26"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="A3:A26"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="A27:A32"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <ignoredErrors>
